--- a/Config/CollectionConfig.xlsx
+++ b/Config/CollectionConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16965" windowHeight="13155"/>
+    <workbookView windowWidth="18270" windowHeight="14775"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1164,9 +1164,9 @@
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="4.01666666666667" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.6" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.0583333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.3833333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.2916666666667" style="2" customWidth="1"/>
-    <col min="6" max="6" width="16.1916666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.65" style="1" customWidth="1"/>
     <col min="7" max="7" width="14.3416666666667" style="1" customWidth="1"/>
     <col min="8" max="8" width="34.75" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>

--- a/Config/CollectionConfig.xlsx
+++ b/Config/CollectionConfig.xlsx
@@ -76,7 +76,7 @@
     <t>品质类型</t>
   </si>
   <si>
-    <t>解锁难度条件</t>
+    <t>解锁条件</t>
   </si>
   <si>
     <t>描述</t>
@@ -1164,7 +1164,7 @@
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="4.01666666666667" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.6" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.3833333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.2916666666667" style="2" customWidth="1"/>
     <col min="6" max="6" width="15.65" style="1" customWidth="1"/>
     <col min="7" max="7" width="14.3416666666667" style="1" customWidth="1"/>
